--- a/artfynd/A 73325-2021 artfynd.xlsx
+++ b/artfynd/A 73325-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73325-2021 artfynd.xlsx
+++ b/artfynd/A 73325-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>69506560</v>
       </c>
       <c r="B2" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639146.395232714</v>
+        <v>639146</v>
       </c>
       <c r="R2" t="n">
-        <v>6712009.716476385</v>
+        <v>6712010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2005-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -806,50 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69551414</v>
+        <v>127797873</v>
       </c>
       <c r="B3" t="n">
-        <v>88933</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>256335</v>
+        <v>2058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandbrändan 9,5 km NV om Västlands kyrka, Upl</t>
+          <t>Sandbrändan, Sandbrändan, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639090.0310395061</v>
+        <v>639113</v>
       </c>
       <c r="R3" t="n">
-        <v>6712011.980291953</v>
+        <v>6712125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,27 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-08-30</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-08-30</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 m lång sträng i äldre granskog.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,21 +882,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre granskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Andreas Öster, Cajsa Björkén, Anton Björk, Cajsa Björkén, Anton Björk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -931,12 +901,7 @@
         <v>81679426</v>
       </c>
       <c r="B4" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639259.8814226071</v>
+        <v>639260</v>
       </c>
       <c r="R4" t="n">
-        <v>6712023.949147414</v>
+        <v>6712024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,19 +966,9 @@
           <t>2019-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1042,6 +997,230 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75726562</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandbrändan 9,5 km NV om Västlands kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>639056</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6712057</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2005-10-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2005-10-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På stammar av minst 20 levande granar, varav en 139 år gammal.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stammar av levande granar. # Gran</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69551414</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sandbrändan 9,5 km NV om Västlands kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>639090</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6712012</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västland</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2005-08-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2005-08-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 m lång sträng i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73325-2021 artfynd.xlsx
+++ b/artfynd/A 73325-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506560</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127797873</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81679426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75726562</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,8 +1246,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69551414</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>